--- a/data/trans_orig/IP31KM16_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM16_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57904</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52618</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59793</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>64279</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48968</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70602</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>52914</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65986</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73937</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>110818</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113507</t>
+          <t>105392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143240</t>
+          <t>113589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14174</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8448</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21522</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11702</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4968</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19498</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37884</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100777</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93429</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106503</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>113947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106151</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120681</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>111081</t>
+          <t>87743</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102696</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116612</t>
+          <t>92364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>225027</t>
+          <t>188520</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214187</t>
+          <t>178815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234528</t>
+          <t>196358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5506</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2774</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9497</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54875</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56681</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50046</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46055</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52778</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61873</t>
+          <t>48754</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57626</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63921</t>
+          <t>51293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111919</t>
+          <t>103628</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>99447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115500</t>
+          <t>107195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17023</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37231</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15328</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9202</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22093</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44187</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35041</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68214</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52793</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32585</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62155</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>54354</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47589</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>60480</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55654</t>
+          <t>54987</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31180</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>60593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>107780</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76835</t>
+          <t>87060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121397</t>
+          <t>119150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3738</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4586</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5182</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37370</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34180</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38964</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>32952</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>30462</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34046</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>30784</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>38496</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>35537</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40130</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>87,27%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>132</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>71448</t>
+          <t>71416</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67829</t>
+          <t>67757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73759</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3456</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5257</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46316</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>43753</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>42367</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>42509</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>39033</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>43894</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>52712</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>49656</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>43961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>95079</t>
+          <t>88825</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91299</t>
+          <t>85327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>90588</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>34521</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>25206</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>43970</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>24,56%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>28197</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20805</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36639</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>63717</t>
+          <t>61869</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51713</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>75421</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>106050</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>96601</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>115365</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>75,44%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>82,07%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>95499</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>87057</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>102891</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>77,2%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>70,38%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>83,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>119524</t>
+          <t>94475</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108516</t>
+          <t>85790</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128579</t>
+          <t>101743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>215023</t>
+          <t>200525</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>200447</t>
+          <t>186973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>227027</t>
+          <t>211465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13983</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8636</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>21564</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>15193</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9691</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>22229</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21225</t>
+          <t>23030</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>29724</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>41184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>143153</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>135572</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>148500</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>91,1%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>113472</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>106436</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>118974</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>82,72%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>139779</t>
+          <t>122159</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132934</t>
+          <t>114870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144989</t>
+          <t>128475</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>253249</t>
+          <t>265312</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>244549</t>
+          <t>253852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>261001</t>
+          <t>273199</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>87588</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>70780</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>112471</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>86218</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>69400</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>107035</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>76109</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130845</t>
+          <t>96009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168208</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154711</t>
+          <t>145236</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>215729</t>
+          <t>195757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>599236</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>574353</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>616044</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>83,62%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>89,69%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>566916</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>546099</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>583734</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>650972</t>
+          <t>537587</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>613888</t>
+          <t>522199</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>668624</t>
+          <t>550680</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1217888</t>
+          <t>1136823</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1182138</t>
+          <t>1109274</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1243156</t>
+          <t>1159795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
